--- a/daily_matches/job_matches_2026-08-30.xlsx
+++ b/daily_matches/job_matches_2026-08-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Engineer II, Data (Cloud &amp; AI)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kearney, NE, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,507 +486,87 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
+          <t>Generative AI, RAG, Prompt Engineering, S3, Glue, Athena, CI/CD, Terraform, Git, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae9405dc478084f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ed8a1f209612e2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
+          <t>RAG, Synapse, Databricks, PySpark, Hadoop, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc099d426154e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=c9493a61af734ed1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Data Science Senior Associate- Card Data &amp; Analytics team</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
+          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6982f28b9756d95</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4728d485fd82b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Grand Island, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8a860e6f7c99c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4aab656d0ca3d815</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b710a7f0b803f961</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Data Scientist - 0034641</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Manpower Internal</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, MLflow, CI/CD, Git, Snowflake, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c7df280aa9cbba</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sr Databricks Data Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Rosslyn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, Apache Airflow, CI/CD, Jenkins, Git, Databricks, PySpark, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab555e988dd3c5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AI FinOps Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>T. Rowe Price</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Owings Mills, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Azure ML, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea9a18422648b58</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Engineer, Cyber Defense Center</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Volvo Group</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Greensboro, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, S3, Data Lake, Docker, CI/CD, Terraform, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7872403091d64ed7</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer III</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Expedia Group</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f243633b12e35cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AI Solutions Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b197fff47f26e6ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ron turley associates</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Glendale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Kafka, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4875b61328aee0d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer Graduate (E-Commerce Knowledge Graph) - 2027 Start</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Hadoop, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d48c33c982fbf5</t>
+          <t>https://www.indeed.com/viewjob?jk=c16698583bc53709</t>
         </is>
       </c>
     </row>
